--- a/data/externalStats/File1/RPT_RPT6764446272771DP_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT6764446272771DP_externalStats.xlsx
@@ -2063,7 +2063,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.9344535459557</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -2104,7 +2104,7 @@
         <v>4485152.572008871</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>6502.991610080125</v>
+        <v>6502.991610080124</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>846073.3380457358</v>
+        <v>846073.338045736</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>189.4409895539809</v>
@@ -2246,19 +2246,19 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>DUPIXENT</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>679878.5839865609</v>
+        <v>684422.7708810191</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>580.7009912939548</v>
+        <v>1210.913003344472</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2323,19 +2323,19 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>DUPIXENT</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>677207.9276767308</v>
+        <v>679878.583986561</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>1210.913003344472</v>
+        <v>580.7009912939548</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -2448,7 +2448,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.33962679615498</v>
+        <v>55.339626796155</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>419510.3093998954</v>
+        <v>429443.7322041095</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>682.8589505041771</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>369204.0737019849</v>
+        <v>369203.9793716841</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>45.78173533647929</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>209442.1559317685</v>
+        <v>210371.4937812766</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>183.2779633371303</v>
@@ -2961,7 +2961,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.4</v>
+        <v>35656.39999999999</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>170528.9488408967</v>
+        <v>172281.3520092994</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>389.2615316687251</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>129751.9026922709</v>
+        <v>129444.4343937071</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1776.792378096958</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>126711.7881352351</v>
+        <v>127944.8341084108</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>326.6424257603529</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>123692.8952123425</v>
+        <v>125277.0213415272</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>41.55721261714001</v>
+        <v>41.55721261714</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>96892.06482839258</v>
+        <v>96889.64743070594</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>204.0127137102595</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>89156.51739221008</v>
+        <v>89156.43953930793</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>238.3357959989694</v>
@@ -3553,7 +3553,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.88</v>
+        <v>72790.87999999999</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>2605823.243804509</v>
+        <v>2605823.149474208</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>612.6259182172483</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>865392.9287808395</v>
+        <v>874429.2554774509</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>1746.424073544983</v>
@@ -3911,7 +3911,7 @@
         <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>419510.3093998954</v>
+        <v>429443.7322041096</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>683.223513430522</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>333135.0511441109</v>
+        <v>335648.5151228039</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>224.8351759542703</v>
@@ -4085,7 +4085,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -4097,7 +4097,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>246815.7446957154</v>
+        <v>246812.7075960777</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>457.5545255467092</v>
@@ -4235,13 +4235,13 @@
         <v>1050.980920266796</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>13.46605752084746</v>
+        <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366343</v>
+        <v>2850.466064366342</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -4256,7 +4256,7 @@
         <v>41.68803870239996</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>177440.4411103505</v>
+        <v>179197.8234781931</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>462.5086911719521</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>138733.8542680717</v>
+        <v>138404.1071528391</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>1894.11775226041</v>
@@ -4553,25 +4553,25 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.77049067758</v>
+        <v>3475.770490677581</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062586</v>
+        <v>40.88056000062585</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798606</v>
+        <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310844</v>
+        <v>4130.131957310843</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250133</v>
+        <v>2671.817886250132</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
@@ -4580,7 +4580,7 @@
         <v>91.05240222120837</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423986</v>
+        <v>6947.472394423984</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>4273.151023763351</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>103405.4005139752</v>
+        <v>104126.4002049236</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>272.1384864083959</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>89156.51739221008</v>
+        <v>89156.43953930793</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>330.5085322076429</v>
@@ -4718,37 +4718,37 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988212</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171316</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132965</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2417.81772495829</v>
+        <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5515.766545076101</v>
+        <v>5515.766545076104</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652559</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.677575700378</v>
+        <v>2919.677575700376</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547174</v>
@@ -4757,7 +4757,7 @@
         <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626164</v>
+        <v>6552.046440626163</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>80039.75796134165</v>
+        <v>81733.85944173264</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>130.8563425551474</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>72931.70031895791</v>
+        <v>73409.45819592112</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>178.1609603833926</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>72802.40999988052</v>
+        <v>73146.3090460755</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>229.4341204836981</v>
@@ -5051,7 +5051,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814804</v>
+        <v>22.34085682814803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>71547.41384323816</v>
+        <v>72979.47865110426</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>108.1413547605109</v>
@@ -5129,7 +5129,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -5138,13 +5138,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229324</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -5153,13 +5153,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>31130.44849219061</v>
+        <v>31130.44849219062</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8685.739662325754</v>
+        <v>8685.739662325752</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -5336,7 +5336,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765181</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -5604,7 +5604,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755257</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -5613,7 +5613,7 @@
         <v>65.4194226827352</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>19.05646504017928</v>
+        <v>19.05646504017929</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>9732.017604071891</v>
@@ -5625,7 +5625,7 @@
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544811</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -5643,7 +5643,7 @@
         <v>96.66477524674978</v>
       </c>
       <c r="Y75" s="131" t="n">
-        <v>21.82725051307307</v>
+        <v>21.82725051307308</v>
       </c>
       <c r="Z75" s="132" t="n">
         <v>13518.77170552647</v>
@@ -5884,13 +5884,13 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557342</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845831</v>
+        <v>2663.397921845832</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -6541,13 +6541,13 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -6693,7 +6693,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -6809,7 +6809,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -6830,7 +6830,7 @@
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888922</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -7077,7 +7077,7 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.3390405849</v>
+        <v>5685.339040584902</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>4472.570348548972</v>
@@ -7092,13 +7092,13 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778223</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>65.60802877947431</v>
+        <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>118.6178170830754</v>
@@ -7235,7 +7235,7 @@
         <v>40.46397792001835</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>232.0624315905734</v>
+        <v>232.0624315905739</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>5516.475815382215</v>
@@ -7244,7 +7244,7 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700363</v>
+        <v>2919.677575700334</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
@@ -7253,7 +7253,7 @@
         <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484156</v>
+        <v>6552.808706484127</v>
       </c>
     </row>
     <row r="100">
@@ -7492,7 +7492,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -7574,7 +7574,7 @@
         <v>3786.655283214763</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>2522.142516424841</v>
+        <v>2522.142516424842</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>496003.1315489453</v>
@@ -7583,7 +7583,7 @@
         <v>251737.4793724213</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>246547.2494316064</v>
+        <v>246547.2494316063</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>3845.468296768772</v>
@@ -7592,7 +7592,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764177</v>
+        <v>504879.6948764176</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8587,7 +8587,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.9344535459557</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -8664,7 +8664,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>877200.3253680117</v>
+        <v>877200.3253680116</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>720.7293338956135</v>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>736828.287210354</v>
+        <v>744415.3999145555</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>1266.711874538585</v>
@@ -8972,7 +8972,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.33962679615498</v>
+        <v>55.339626796155</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -9013,7 +9013,7 @@
         <v>581866.6305464627</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>849.15899935381</v>
+        <v>849.1589993538101</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>486922.565243347</v>
+        <v>486922.4304369448</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>55.47601779397878</v>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>435934.6865114004</v>
+        <v>445931.5006802402</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>684.9758132507402</v>
+        <v>684.9758132507401</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>225886.7582405971</v>
+        <v>226853.0700598022</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>189.0163963692158</v>
@@ -9485,7 +9485,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.4</v>
+        <v>35656.39999999999</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>186498.4535839301</v>
+        <v>188350.7026413401</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>407.19870304802</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>153880.4292792708</v>
+        <v>153474.3899276184</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1820.8212932262</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>136607.3836804389</v>
+        <v>137885.5031566595</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>336.8254182951961</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>132594.5039227127</v>
+        <v>134239.4484451662</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>42.85836894418266</v>
@@ -9893,7 +9893,7 @@
         <v>127272.8777518657</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>396.1830231832591</v>
+        <v>396.183023183259</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>110336.8907090594</v>
+        <v>110333.5183723862</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>220.4806199609516</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>98056.03823815229</v>
+        <v>98055.96733001938</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>244.5277599790226</v>
@@ -10077,7 +10077,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.88</v>
+        <v>72790.87999999999</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>2960367.431643226</v>
+        <v>2960367.296836824</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>658.3602571987988</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>942548.3301733349</v>
+        <v>952060.7077232818</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>1816.7771680026</v>
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>877200.3253680117</v>
+        <v>877200.3253680116</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>726.2533367258894</v>
+        <v>726.2533367258893</v>
       </c>
     </row>
     <row r="53">
@@ -10435,7 +10435,7 @@
         <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -10444,7 +10444,7 @@
         <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>435934.6865114004</v>
+        <v>445931.5006802402</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>685.0910599231772</v>
+        <v>685.0910599231773</v>
       </c>
     </row>
     <row r="54">
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>358481.2621633098</v>
+        <v>361092.5185049685</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>231.8747653133985</v>
@@ -10609,7 +10609,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -10621,7 +10621,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>280679.4835727784</v>
+        <v>280674.9252560166</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>494.4883268488395</v>
@@ -10759,13 +10759,13 @@
         <v>1050.980920266796</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>13.46605752084746</v>
+        <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366343</v>
+        <v>2850.466064366342</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -10780,7 +10780,7 @@
         <v>41.68803870239996</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
@@ -10802,14 +10802,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>164533.3757342851</v>
+        <v>164235.0823963753</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>1941.053990161422</v>
+        <v>1565.744525013994</v>
       </c>
     </row>
     <row r="58">
@@ -10883,14 +10883,14 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>BASAL INSULIN</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>164235.0823963753</v>
+        <v>164097.9152152537</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>1565.744525013994</v>
+        <v>1941.053990161422</v>
       </c>
     </row>
     <row r="59">
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>159535.3306726604</v>
+        <v>160871.151800584</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>381.6103836297689</v>
@@ -11077,25 +11077,25 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.77049067758</v>
+        <v>3475.770490677581</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062586</v>
+        <v>40.88056000062585</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798606</v>
+        <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310844</v>
+        <v>4130.131957310843</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250133</v>
+        <v>2671.817886250132</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
@@ -11104,7 +11104,7 @@
         <v>91.05240222120837</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423986</v>
+        <v>6947.472394423984</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>4273.151023763351</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>108687.8530543995</v>
+        <v>109416.9559010975</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>269.4497581626809</v>
@@ -11207,14 +11207,14 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>98056.03823815229</v>
+        <v>98204.64491452638</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>337.7628504760763</v>
+        <v>147.5496861749075</v>
       </c>
     </row>
     <row r="63">
@@ -11242,37 +11242,37 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988212</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171316</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132965</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2417.81772495829</v>
+        <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5515.766545076101</v>
+        <v>5515.766545076104</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652559</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.677575700378</v>
+        <v>2919.677575700376</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547174</v>
@@ -11281,21 +11281,21 @@
         <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626164</v>
+        <v>6552.046440626163</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>96255.91750821355</v>
+        <v>98055.96733001938</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>147.5496861749075</v>
+        <v>337.7628504760763</v>
       </c>
     </row>
     <row r="64">
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>81947.85857459124</v>
+        <v>83150.24558853626</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>194.7526152822731</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>75607.91733017538</v>
+        <v>77072.00421733106</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>107.3919351720206</v>
@@ -11575,7 +11575,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814804</v>
+        <v>22.34085682814803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>72214.99113430768</v>
+        <v>72672.01399288405</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>165.7698655887277</v>
@@ -11653,7 +11653,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -11662,13 +11662,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229324</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -11677,13 +11677,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>31130.44849219061</v>
+        <v>31130.44849219062</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8685.739662325754</v>
+        <v>8685.739662325752</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -11860,7 +11860,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765181</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -12128,7 +12128,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755257</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -12137,7 +12137,7 @@
         <v>65.4194226827352</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>19.05646504017928</v>
+        <v>19.05646504017929</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>9732.017604071891</v>
@@ -12149,7 +12149,7 @@
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544811</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -12167,7 +12167,7 @@
         <v>96.66477524674978</v>
       </c>
       <c r="Y75" s="131" t="n">
-        <v>21.82725051307307</v>
+        <v>21.82725051307308</v>
       </c>
       <c r="Z75" s="132" t="n">
         <v>13518.77170552647</v>
@@ -12408,13 +12408,13 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557342</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845831</v>
+        <v>2663.397921845832</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -13065,13 +13065,13 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -13217,7 +13217,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -13229,7 +13229,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -13333,7 +13333,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -13354,7 +13354,7 @@
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888922</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -13601,7 +13601,7 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.3390405849</v>
+        <v>5685.339040584902</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>4472.570348548972</v>
@@ -13616,13 +13616,13 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778223</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>65.60802877947431</v>
+        <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>118.6178170830754</v>
@@ -13759,7 +13759,7 @@
         <v>40.46397792001835</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>232.0624315905734</v>
+        <v>232.0624315905739</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>5516.475815382215</v>
@@ -13768,7 +13768,7 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700363</v>
+        <v>2919.677575700334</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
@@ -13777,7 +13777,7 @@
         <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484156</v>
+        <v>6552.808706484127</v>
       </c>
     </row>
     <row r="100">
@@ -14016,7 +14016,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -14098,7 +14098,7 @@
         <v>3786.655283214763</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>2522.142516424841</v>
+        <v>2522.142516424842</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>496003.1315489453</v>
@@ -14107,7 +14107,7 @@
         <v>251737.4793724213</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>246547.2494316064</v>
+        <v>246547.2494316063</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>3845.468296768772</v>
@@ -14116,7 +14116,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764177</v>
+        <v>504879.6948764176</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15111,7 +15111,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.9344535459557</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7105821.769012145</v>
+        <v>7105821.769012148</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>9754.527377416774</v>
+        <v>9754.527377416773</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15188,7 +15188,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -15229,7 +15229,7 @@
         <v>1111025.52965187</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>867.3273413215643</v>
+        <v>867.3273413215642</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>817655.5870260906</v>
+        <v>825753.80794682</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1325.081957717323</v>
@@ -15496,7 +15496,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.33962679615498</v>
+        <v>55.339626796155</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -15537,7 +15537,7 @@
         <v>667647.1117400256</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>942.5664892827293</v>
+        <v>942.5664892827294</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>636675.2538853276</v>
+        <v>636675.0714767276</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>66.11298944579626</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>459311.5650294687</v>
+        <v>469493.7465130611</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>685.3046016411006</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>248969.0182800351</v>
+        <v>249989.5853107493</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>194.7114603918203</v>
@@ -16009,7 +16009,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.4</v>
+        <v>35656.39999999999</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>208180.2065232188</v>
+        <v>210168.6806130857</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>425.9624192844726</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>180130.6978277591</v>
+        <v>179632.3232812029</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>1865.941244872346</v>
@@ -16260,10 +16260,10 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>149587.3191428244</v>
+        <v>150933.0726620579</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>345.2595267693078</v>
+        <v>345.2595267693077</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>144795.4104438485</v>
+        <v>146527.7963772771</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>44.14969160047089</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>127397.5844974043</v>
+        <v>127393.1963711188</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>237.6692890931074</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>108267.1331581201</v>
+        <v>108267.0672107891</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>251.9589586047851</v>
@@ -16601,7 +16601,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.88</v>
+        <v>72790.87999999999</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>7773468.88075217</v>
+        <v>7773468.880752171</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>10697.0938666995</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3392622.675628973</v>
+        <v>3392622.493220373</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>707.4068275609241</v>
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1047250.705007625</v>
+        <v>1057415.785351566</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1900.49425990416</v>
@@ -16959,7 +16959,7 @@
         <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -16968,7 +16968,7 @@
         <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>459311.5650294687</v>
+        <v>469493.746513061</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>685.3351048132804</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>393764.4287238837</v>
+        <v>396517.3816880264</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>238.8611519922912</v>
@@ -17133,7 +17133,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -17157,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>322144.9574340167</v>
+        <v>322139.0258696457</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>533.0386368099751</v>
@@ -17283,13 +17283,13 @@
         <v>1050.980920266796</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>13.46605752084746</v>
+        <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366343</v>
+        <v>2850.466064366342</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -17304,7 +17304,7 @@
         <v>41.68803870239996</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>192602.1549782877</v>
+        <v>192067.6687571068</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>1989.153308037623</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>175160.2499163294</v>
+        <v>176568.5153732982</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>376.6070963834845</v>
@@ -17601,25 +17601,25 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.77049067758</v>
+        <v>3475.770490677581</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062586</v>
+        <v>40.88056000062585</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798606</v>
+        <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310844</v>
+        <v>4130.131957310843</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250133</v>
+        <v>2671.817886250132</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
@@ -17628,7 +17628,7 @@
         <v>91.05240222120837</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423986</v>
+        <v>6947.472394423984</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>4273.151023763351</v>
@@ -17654,10 +17654,10 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>119708.149072745</v>
+        <v>121423.5980554174</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>272.6536613951824</v>
+        <v>272.6536613951823</v>
       </c>
     </row>
     <row r="62">
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>116863.9439162867</v>
+        <v>119136.3874538897</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>166.0435638400704</v>
@@ -17766,37 +17766,37 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988212</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171316</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132965</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2417.81772495829</v>
+        <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5515.766545076101</v>
+        <v>5515.766545076104</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652559</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.677575700378</v>
+        <v>2919.677575700376</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547174</v>
@@ -17805,7 +17805,7 @@
         <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626164</v>
+        <v>6552.046440626163</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>116403.0799159494</v>
+        <v>117152.0213203908</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>266.7875945520336</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>108267.1331581201</v>
+        <v>108267.0672107891</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>347.5927466644546</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>64747.84486588681</v>
+        <v>65141.46164711809</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>145.8247890034719</v>
@@ -18099,7 +18099,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814804</v>
+        <v>22.34085682814803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>47165.57297158396</v>
+        <v>48450.48612583289</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>43.81252004427874</v>
@@ -18177,7 +18177,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -18186,13 +18186,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229324</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -18201,13 +18201,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>31130.44849219061</v>
+        <v>31130.44849219062</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8685.739662325754</v>
+        <v>8685.739662325752</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>40666.67841360749</v>
+        <v>41016.72635325958</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>45.41890275507653</v>
@@ -18384,7 +18384,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765181</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -18652,7 +18652,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755257</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -18661,7 +18661,7 @@
         <v>65.4194226827352</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>19.05646504017928</v>
+        <v>19.05646504017929</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>9732.017604071891</v>
@@ -18673,7 +18673,7 @@
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544811</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -18691,7 +18691,7 @@
         <v>96.66477524674978</v>
       </c>
       <c r="Y75" s="131" t="n">
-        <v>21.82725051307307</v>
+        <v>21.82725051307308</v>
       </c>
       <c r="Z75" s="132" t="n">
         <v>13518.77170552647</v>
@@ -18932,13 +18932,13 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557342</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845831</v>
+        <v>2663.397921845832</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -19589,13 +19589,13 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -19753,7 +19753,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -19765,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -19857,7 +19857,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -19878,7 +19878,7 @@
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888922</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -20125,7 +20125,7 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.3390405849</v>
+        <v>5685.339040584902</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>4472.570348548972</v>
@@ -20140,13 +20140,13 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778223</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>65.60802877947431</v>
+        <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>118.6178170830754</v>
@@ -20283,7 +20283,7 @@
         <v>40.46397792001835</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>232.0624315905734</v>
+        <v>232.0624315905739</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>5516.475815382215</v>
@@ -20292,7 +20292,7 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700363</v>
+        <v>2919.677575700334</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
@@ -20301,7 +20301,7 @@
         <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484156</v>
+        <v>6552.808706484127</v>
       </c>
     </row>
     <row r="100">
@@ -20540,7 +20540,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -20622,7 +20622,7 @@
         <v>3786.655283214763</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>2522.142516424841</v>
+        <v>2522.142516424842</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>496003.1315489453</v>
@@ -20631,7 +20631,7 @@
         <v>251737.4793724213</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>246547.2494316064</v>
+        <v>246547.2494316063</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>3845.468296768772</v>
@@ -20640,7 +20640,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764177</v>
+        <v>504879.6948764176</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21635,7 +21635,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.9344535459557</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -21712,7 +21712,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>898145.1573016972</v>
+        <v>898145.1573016973</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>203.2628537277481</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>885198.5801426525</v>
+        <v>893766.5419408984</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1386.141734328937</v>
@@ -22020,7 +22020,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.33962679615498</v>
+        <v>55.339626796155</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>819567.4030125161</v>
+        <v>819567.1701250562</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>78.27976289350613</v>
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>231.9442520381598</v>
+        <v>231.9442520381599</v>
       </c>
     </row>
     <row r="31">
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>759244.4032337641</v>
+        <v>759244.4032337639</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1046.24880310383</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>472520.9039310681</v>
+        <v>482757.4699498476</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>683.0979208238161</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>267138.2275596328</v>
+        <v>268206.8622675232</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>200.1341745637325</v>
@@ -22533,7 +22533,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.4</v>
+        <v>35656.39999999999</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>179322.8916186612</v>
+        <v>180996.8510311545</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>395.8814041868176</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>159998.5222656493</v>
+        <v>161405.3239244144</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>353.9048253196112</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>154168.7353657388</v>
+        <v>155974.5375427666</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>45.37926051154399</v>
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>145231.2791944038</v>
+        <v>145225.6998220094</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>255.2710766433429</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>117360.7576585798</v>
+        <v>117360.6979398984</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>257.0686862852901</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>114154.5372528448</v>
+        <v>115085.9769406809</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>278.106734623086</v>
@@ -23125,7 +23125,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.88</v>
+        <v>72790.87999999999</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3931719.308008743</v>
+        <v>3931719.075121283</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>762.9533459135781</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1084543.580167486</v>
+        <v>1094851.488273029</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1927.909408130234</v>
@@ -23483,7 +23483,7 @@
         <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -23492,7 +23492,7 @@
         <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>472520.9039310681</v>
+        <v>482757.4699498476</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>683.1283257757816</v>
@@ -23657,7 +23657,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>421306.9629253716</v>
+        <v>424181.3998102897</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>245.5134350752765</v>
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>364725.137501135</v>
+        <v>364717.9137711779</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>572.5154782521217</v>
@@ -23807,13 +23807,13 @@
         <v>1050.980920266796</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>13.46605752084746</v>
+        <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366343</v>
+        <v>2850.466064366342</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -23828,7 +23828,7 @@
         <v>41.68803870239996</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>187985.2281656479</v>
+        <v>189458.7919212243</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>380.9868502583004</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>171407.6055129592</v>
+        <v>173840.8646212945</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>381.7151259532553</v>
@@ -24100,7 +24100,7 @@
         <v>162271.5517438948</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>1424.694944294908</v>
+        <v>1424.694944294909</v>
       </c>
     </row>
     <row r="61">
@@ -24125,25 +24125,25 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.77049067758</v>
+        <v>3475.770490677581</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062586</v>
+        <v>40.88056000062585</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798606</v>
+        <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310844</v>
+        <v>4130.131957310843</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250133</v>
+        <v>2671.817886250132</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
@@ -24152,7 +24152,7 @@
         <v>91.05240222120837</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423986</v>
+        <v>6947.472394423984</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>4273.151023763351</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>138566.0071975626</v>
+        <v>141183.4094651651</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>186.2859347078134</v>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>121653.0960962544</v>
+        <v>122416.3665208338</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>264.1517331178595</v>
@@ -24290,37 +24290,37 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988212</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171316</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132965</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2417.81772495829</v>
+        <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5515.766545076101</v>
+        <v>5515.766545076104</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652559</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.677575700378</v>
+        <v>2919.677575700376</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547174</v>
@@ -24329,7 +24329,7 @@
         <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626164</v>
+        <v>6552.046440626163</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>117360.7576585798</v>
+        <v>117360.6979398984</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>354.6331001102211</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>40942.28158345533</v>
+        <v>41286.72607806405</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>43.29829418544201</v>
@@ -24585,14 +24585,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - MISC.</t>
+          <t>VASOACTIVE SGC STIMULATOR</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>37312.77137098507</v>
+        <v>37835.41603889556</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>49.52139328881419</v>
+        <v>47.48465002356028</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -24623,7 +24623,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814804</v>
+        <v>22.34085682814803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -24666,14 +24666,14 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>VASOACTIVE SGC STIMULATOR</t>
+          <t>OPHTHALMICS - MISC.</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>37165.03650118218</v>
+        <v>37488.95703844996</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>47.48465002356028</v>
+        <v>49.52139328881418</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24701,7 +24701,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -24710,13 +24710,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229324</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -24725,13 +24725,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>31130.44849219061</v>
+        <v>31130.44849219062</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8685.739662325754</v>
+        <v>8685.739662325752</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>36089.38489447791</v>
+        <v>36426.12670652315</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>259.5143090597786</v>
@@ -24908,7 +24908,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765181</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -25176,7 +25176,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755257</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -25185,7 +25185,7 @@
         <v>65.4194226827352</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>19.05646504017928</v>
+        <v>19.05646504017929</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>9732.017604071891</v>
@@ -25197,7 +25197,7 @@
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544811</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -25215,7 +25215,7 @@
         <v>96.66477524674978</v>
       </c>
       <c r="Y75" s="131" t="n">
-        <v>21.82725051307307</v>
+        <v>21.82725051307308</v>
       </c>
       <c r="Z75" s="132" t="n">
         <v>13518.77170552647</v>
@@ -25456,13 +25456,13 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557342</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845831</v>
+        <v>2663.397921845832</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -26113,13 +26113,13 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -26265,7 +26265,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -26277,7 +26277,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -26289,7 +26289,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -26381,7 +26381,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -26402,7 +26402,7 @@
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888922</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -26649,7 +26649,7 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.3390405849</v>
+        <v>5685.339040584902</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>4472.570348548972</v>
@@ -26664,13 +26664,13 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778223</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>65.60802877947431</v>
+        <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>118.6178170830754</v>
@@ -26807,7 +26807,7 @@
         <v>40.46397792001835</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>232.0624315905734</v>
+        <v>232.0624315905739</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>5516.475815382215</v>
@@ -26816,7 +26816,7 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700363</v>
+        <v>2919.677575700334</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
@@ -26825,7 +26825,7 @@
         <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484156</v>
+        <v>6552.808706484127</v>
       </c>
     </row>
     <row r="100">
@@ -27064,7 +27064,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -27146,7 +27146,7 @@
         <v>3786.655283214763</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>2522.142516424841</v>
+        <v>2522.142516424842</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>496003.1315489453</v>
@@ -27155,7 +27155,7 @@
         <v>251737.4793724213</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>246547.2494316064</v>
+        <v>246547.2494316063</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>3845.468296768772</v>
@@ -27164,7 +27164,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764177</v>
+        <v>504879.6948764176</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28159,7 +28159,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.9344535459557</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -28236,7 +28236,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1063766.783054913</v>
+        <v>1063766.49708147</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>92.68558765879806</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>959868.005120976</v>
+        <v>969024.9572445255</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1450.015145446814</v>
@@ -28544,7 +28544,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.33962679615498</v>
+        <v>55.339626796155</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>939863.201876877</v>
+        <v>939863.2018768771</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>207.8023572318635</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>872627.0500916672</v>
+        <v>872627.0500916673</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1161.336171445251</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>630970.5459087702</v>
+        <v>630970.5459087703</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>160.1194938565857</v>
@@ -28793,10 +28793,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>488631.7957832391</v>
+        <v>499027.6018197911</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>680.8983455187633</v>
+        <v>680.8983455187636</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>486031.0345344367</v>
+        <v>486031.0345344368</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>88.53256258799576</v>
@@ -28947,10 +28947,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>286660.4489198607</v>
+        <v>287790.8057999549</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>205.7079113253324</v>
+        <v>205.7079113253325</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>249571.0033096265</v>
+        <v>249571.0033096266</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>46.27663763732347</v>
@@ -29057,7 +29057,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.4</v>
+        <v>35656.39999999999</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>167276.3054151864</v>
+        <v>167270.1992136716</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>274.1764525795489</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>164513.3521178053</v>
+        <v>166414.7962048187</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>46.64307291679049</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>161652.4810870978</v>
+        <v>162953.2068707358</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>389.3494284723204</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>128359.5193557328</v>
+        <v>128359.4654394562</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>262.2820392431559</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>119175.8698043119</v>
+        <v>121172.7105505014</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>151.6245874764233</v>
@@ -29649,7 +29649,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.88</v>
+        <v>72790.87999999999</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>4640550.532455193</v>
+        <v>4640550.246481751</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>828.4194522121426</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>968211.6287530202</v>
+        <v>977368.5808765698</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1591.449898611768</v>
@@ -30007,7 +30007,7 @@
         <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
         <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>488631.7957832391</v>
+        <v>499027.6018197911</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>680.9286525667835</v>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>486031.0345344367</v>
+        <v>486031.0345344368</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>124.2025011145804</v>
@@ -30181,7 +30181,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -30193,7 +30193,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -30205,7 +30205,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>451173.801037666</v>
+        <v>454205.6020047735</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>252.3509842421229</v>
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>417303.0069383825</v>
+        <v>417295.3443087898</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>614.9159745714738</v>
@@ -30331,13 +30331,13 @@
         <v>1050.980920266796</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>13.46605752084746</v>
+        <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366343</v>
+        <v>2850.466064366342</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -30352,7 +30352,7 @@
         <v>41.68803870239996</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>246271.9209550729</v>
+        <v>249760.0623491908</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>534.4011763345574</v>
@@ -30462,7 +30462,7 @@
         <v>167560.8225097525</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>462.2325903015173</v>
+        <v>462.2325903015174</v>
       </c>
     </row>
     <row r="59">
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>128359.5193557328</v>
+        <v>128359.4654394562</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>361.8165997639837</v>
@@ -30649,25 +30649,25 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.77049067758</v>
+        <v>3475.770490677581</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062586</v>
+        <v>40.88056000062585</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798606</v>
+        <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310844</v>
+        <v>4130.131957310843</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250133</v>
+        <v>2671.817886250132</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
@@ -30676,7 +30676,7 @@
         <v>91.05240222120837</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423986</v>
+        <v>6947.472394423984</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>4273.151023763351</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>127243.1727910445</v>
+        <v>128030.6438472644</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>261.541913994655</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>119175.8698043119</v>
+        <v>121172.7105505014</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>163.6270054127749</v>
@@ -30814,37 +30814,37 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988212</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171316</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132965</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2417.81772495829</v>
+        <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5515.766545076101</v>
+        <v>5515.766545076104</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652559</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.677575700378</v>
+        <v>2919.677575700376</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547174</v>
@@ -30853,7 +30853,7 @@
         <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626164</v>
+        <v>6552.046440626163</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,7 +30864,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>81326.56259703494</v>
+        <v>81831.51790384474</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>178.3339380167246</v>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>44289.25711314797</v>
+        <v>45072.30406214964</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>53.27350370793251</v>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>41271.22645618688</v>
+        <v>41613.59707700519</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>41.27669682992372</v>
@@ -31147,7 +31147,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814804</v>
+        <v>22.34085682814803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>35085.81839727281</v>
+        <v>35406.02786434698</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>247.3975859697775</v>
@@ -31225,7 +31225,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -31234,13 +31234,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229324</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -31249,13 +31249,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>31130.44849219061</v>
+        <v>31130.44849219062</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8685.739662325754</v>
+        <v>8685.739662325752</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -31275,7 +31275,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>33293.9962283615</v>
+        <v>33594.02408922867</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>159.5085771344216</v>
@@ -31432,7 +31432,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765181</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -31700,7 +31700,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755257</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -31709,7 +31709,7 @@
         <v>65.4194226827352</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>19.05646504017928</v>
+        <v>19.05646504017929</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>9732.017604071891</v>
@@ -31721,7 +31721,7 @@
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544811</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -31739,7 +31739,7 @@
         <v>96.66477524674978</v>
       </c>
       <c r="Y75" s="131" t="n">
-        <v>21.82725051307307</v>
+        <v>21.82725051307308</v>
       </c>
       <c r="Z75" s="132" t="n">
         <v>13518.77170552647</v>
@@ -31980,13 +31980,13 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557342</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845831</v>
+        <v>2663.397921845832</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -32637,13 +32637,13 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>16.81060051458185</v>
+        <v>16.81060051458184</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -32789,7 +32789,7 @@
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833214</v>
+        <v>7.681420291833212</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -32801,7 +32801,7 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -32813,7 +32813,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -32905,7 +32905,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -32926,7 +32926,7 @@
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888922</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -33173,7 +33173,7 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.3390405849</v>
+        <v>5685.339040584902</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>4472.570348548972</v>
@@ -33188,13 +33188,13 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778223</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>65.60802877947431</v>
+        <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>118.6178170830754</v>
@@ -33331,7 +33331,7 @@
         <v>40.46397792001835</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>232.0624315905734</v>
+        <v>232.0624315905739</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>5516.475815382215</v>
@@ -33340,7 +33340,7 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700363</v>
+        <v>2919.677575700334</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
@@ -33349,7 +33349,7 @@
         <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484156</v>
+        <v>6552.808706484127</v>
       </c>
     </row>
     <row r="100">
@@ -33588,7 +33588,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -33670,7 +33670,7 @@
         <v>3786.655283214763</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>2522.142516424841</v>
+        <v>2522.142516424842</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>496003.1315489453</v>
@@ -33679,7 +33679,7 @@
         <v>251737.4793724213</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>246547.2494316064</v>
+        <v>246547.2494316063</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>3845.468296768772</v>
@@ -33688,7 +33688,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764177</v>
+        <v>504879.6948764176</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
